--- a/docs/exports/Formato_Ejecucion_Pruebas_Portal_Proveedores.xlsx
+++ b/docs/exports/Formato_Ejecucion_Pruebas_Portal_Proveedores.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4457" uniqueCount="2101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4466" uniqueCount="2103">
   <si>
     <t>Seccion</t>
   </si>
@@ -6330,6 +6330,12 @@
   </si>
   <si>
     <t>Doble palomita en vista de login "recuerdame"</t>
+  </si>
+  <si>
+    <t>Aprobado</t>
+  </si>
+  <si>
+    <t>Redondear dias en tag de Detalle RFQ</t>
   </si>
 </sst>
 </file>
@@ -6349,7 +6355,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6360,6 +6366,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -6375,7 +6387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6386,6 +6398,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6401,6 +6417,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1524206</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>885933</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4229100" y="304800"/>
+          <a:ext cx="1476581" cy="771633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16254,302 +16313,318 @@
       </c>
       <c r="I351" s="2"/>
     </row>
-    <row r="352" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A352" s="2" t="s">
+    <row r="352" spans="1:9" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
         <v>1246</v>
       </c>
-      <c r="B352" s="2" t="s">
+      <c r="B352" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C352" s="2" t="s">
+      <c r="C352" s="4" t="s">
         <v>1247</v>
       </c>
-      <c r="D352" s="2" t="s">
+      <c r="D352" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="E352" s="2" t="s">
+      <c r="E352" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="F352" s="2" t="s">
+      <c r="F352" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="G352" s="2" t="s">
+      <c r="G352" s="4" t="s">
         <v>1251</v>
       </c>
-      <c r="H352" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I352" s="2"/>
-    </row>
-    <row r="353" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A353" s="2" t="s">
+      <c r="H352" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
         <v>1246</v>
       </c>
-      <c r="B353" s="2" t="s">
+      <c r="B353" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C353" s="2" t="s">
+      <c r="C353" s="4" t="s">
         <v>1247</v>
       </c>
-      <c r="D353" s="2" t="s">
+      <c r="D353" s="4" t="s">
         <v>1252</v>
       </c>
-      <c r="E353" s="2" t="s">
+      <c r="E353" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="F353" s="2" t="s">
+      <c r="F353" s="4" t="s">
         <v>1253</v>
       </c>
-      <c r="G353" s="2" t="s">
+      <c r="G353" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="H353" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I353" s="2"/>
-    </row>
-    <row r="354" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A354" s="2" t="s">
+      <c r="H353" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I353" s="4" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
         <v>1246</v>
       </c>
-      <c r="B354" s="2" t="s">
+      <c r="B354" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C354" s="2" t="s">
+      <c r="C354" s="4" t="s">
         <v>1247</v>
       </c>
-      <c r="D354" s="2" t="s">
+      <c r="D354" s="4" t="s">
         <v>1255</v>
       </c>
-      <c r="E354" s="2" t="s">
+      <c r="E354" s="4" t="s">
         <v>1256</v>
       </c>
-      <c r="F354" s="2" t="s">
+      <c r="F354" s="4" t="s">
         <v>1257</v>
       </c>
-      <c r="G354" s="2" t="s">
+      <c r="G354" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="H354" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I354" s="2"/>
+      <c r="H354" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I354" s="4" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="355" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A355" s="2" t="s">
+      <c r="A355" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="B355" s="2" t="s">
+      <c r="B355" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C355" s="2" t="s">
+      <c r="C355" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="D355" s="2" t="s">
+      <c r="D355" s="4" t="s">
         <v>1261</v>
       </c>
-      <c r="E355" s="2" t="s">
+      <c r="E355" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="F355" s="2" t="s">
+      <c r="F355" s="4" t="s">
         <v>1263</v>
       </c>
-      <c r="G355" s="2" t="s">
+      <c r="G355" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="H355" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I355" s="2"/>
+      <c r="H355" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I355" s="4" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="356" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A356" s="2" t="s">
+      <c r="A356" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C356" s="2" t="s">
+      <c r="C356" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="D356" s="2" t="s">
+      <c r="D356" s="4" t="s">
         <v>1265</v>
       </c>
-      <c r="E356" s="2" t="s">
+      <c r="E356" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="F356" s="2" t="s">
+      <c r="F356" s="4" t="s">
         <v>1266</v>
       </c>
-      <c r="G356" s="2" t="s">
+      <c r="G356" s="4" t="s">
         <v>1267</v>
       </c>
-      <c r="H356" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I356" s="2"/>
-    </row>
-    <row r="357" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A357" s="2" t="s">
+      <c r="H356" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I356" s="4" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A357" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="B357" s="2" t="s">
+      <c r="B357" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C357" s="2" t="s">
+      <c r="C357" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="D357" s="2" t="s">
+      <c r="D357" s="4" t="s">
         <v>1268</v>
       </c>
-      <c r="E357" s="2" t="s">
+      <c r="E357" s="4" t="s">
         <v>1269</v>
       </c>
-      <c r="F357" s="2" t="s">
+      <c r="F357" s="4" t="s">
         <v>1270</v>
       </c>
-      <c r="G357" s="2" t="s">
+      <c r="G357" s="4" t="s">
         <v>1271</v>
       </c>
-      <c r="H357" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I357" s="2"/>
+      <c r="H357" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I357" s="4" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="358" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A358" s="2" t="s">
+      <c r="A358" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="B358" s="2" t="s">
+      <c r="B358" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C358" s="2" t="s">
+      <c r="C358" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="D358" s="2" t="s">
+      <c r="D358" s="4" t="s">
         <v>1272</v>
       </c>
-      <c r="E358" s="2" t="s">
+      <c r="E358" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="F358" s="2" t="s">
+      <c r="F358" s="4" t="s">
         <v>1273</v>
       </c>
-      <c r="G358" s="2" t="s">
+      <c r="G358" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="H358" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I358" s="2"/>
+      <c r="H358" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I358" s="4" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="359" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A359" s="2" t="s">
+      <c r="A359" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="B359" s="2" t="s">
+      <c r="B359" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C359" s="2" t="s">
+      <c r="C359" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="D359" s="2" t="s">
+      <c r="D359" s="4" t="s">
         <v>1275</v>
       </c>
-      <c r="E359" s="2" t="s">
+      <c r="E359" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="F359" s="2" t="s">
+      <c r="F359" s="4" t="s">
         <v>1276</v>
       </c>
-      <c r="G359" s="2" t="s">
+      <c r="G359" s="4" t="s">
         <v>1277</v>
       </c>
-      <c r="H359" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I359" s="2"/>
+      <c r="H359" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I359" s="4" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="360" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A360" s="2" t="s">
+      <c r="A360" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="B360" s="2" t="s">
+      <c r="B360" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C360" s="2" t="s">
+      <c r="C360" s="4" t="s">
         <v>1279</v>
       </c>
-      <c r="D360" s="2" t="s">
+      <c r="D360" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="E360" s="2" t="s">
+      <c r="E360" s="4" t="s">
         <v>1281</v>
       </c>
-      <c r="F360" s="2" t="s">
+      <c r="F360" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="G360" s="2" t="s">
+      <c r="G360" s="4" t="s">
         <v>1283</v>
       </c>
-      <c r="H360" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I360" s="2"/>
+      <c r="H360" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I360" s="4"/>
     </row>
     <row r="361" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A361" s="2" t="s">
+      <c r="A361" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="B361" s="2" t="s">
+      <c r="B361" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C361" s="2" t="s">
+      <c r="C361" s="4" t="s">
         <v>1279</v>
       </c>
-      <c r="D361" s="2" t="s">
+      <c r="D361" s="4" t="s">
         <v>1284</v>
       </c>
-      <c r="E361" s="2" t="s">
+      <c r="E361" s="4" t="s">
         <v>1281</v>
       </c>
-      <c r="F361" s="2" t="s">
+      <c r="F361" s="4" t="s">
         <v>1285</v>
       </c>
-      <c r="G361" s="2" t="s">
+      <c r="G361" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="H361" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I361" s="2"/>
+      <c r="H361" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I361" s="4"/>
     </row>
     <row r="362" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A362" s="2" t="s">
+      <c r="A362" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="B362" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="C362" s="4" t="s">
         <v>1279</v>
       </c>
-      <c r="D362" s="2" t="s">
+      <c r="D362" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="E362" s="2" t="s">
+      <c r="E362" s="4" t="s">
         <v>1281</v>
       </c>
-      <c r="F362" s="2" t="s">
+      <c r="F362" s="4" t="s">
         <v>1287</v>
       </c>
-      <c r="G362" s="2" t="s">
+      <c r="G362" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="H362" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I362" s="2"/>
+      <c r="H362" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I362" s="4"/>
     </row>
     <row r="363" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
@@ -21794,10 +21869,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -21805,7 +21881,13 @@
         <v>2100</v>
       </c>
     </row>
+    <row r="2" spans="1:1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/exports/Formato_Ejecucion_Pruebas_Portal_Proveedores.xlsx
+++ b/docs/exports/Formato_Ejecucion_Pruebas_Portal_Proveedores.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4466" uniqueCount="2103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4472" uniqueCount="2109">
   <si>
     <t>Seccion</t>
   </si>
@@ -6336,6 +6336,24 @@
   </si>
   <si>
     <t>Redondear dias en tag de Detalle RFQ</t>
+  </si>
+  <si>
+    <t>Se rompe flujo al cancelar el rfq</t>
+  </si>
+  <si>
+    <t>Solo requisitor deberia ver sus reqs</t>
+  </si>
+  <si>
+    <t>Al crear usuario poner roles en espanol</t>
+  </si>
+  <si>
+    <t>Agregar buscador a los select</t>
+  </si>
+  <si>
+    <t>Se agrego Modal de Ver requisicion para compras</t>
+  </si>
+  <si>
+    <t>Cambiar categoria por subcategoria y ponerla hasta arriba</t>
   </si>
 </sst>
 </file>
@@ -6387,7 +6405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6402,6 +6420,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6451,6 +6475,120 @@
         <a:xfrm>
           <a:off x="4229100" y="304800"/>
           <a:ext cx="1476581" cy="771633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>942974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>14858</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4236400" y="1533524"/>
+          <a:ext cx="2793050" cy="1434084"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4171950</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>352922</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>82</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4171950" y="3552825"/>
+          <a:ext cx="3562847" cy="590632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9692</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>581657</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>20188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4191167" y="4162425"/>
+          <a:ext cx="3772365" cy="2801488"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21869,21 +22007,51 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>2100</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>2102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="5" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2108</v>
       </c>
     </row>
   </sheetData>

--- a/docs/exports/Formato_Ejecucion_Pruebas_Portal_Proveedores.xlsx
+++ b/docs/exports/Formato_Ejecucion_Pruebas_Portal_Proveedores.xlsx
@@ -23,11 +23,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resumen!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4472" uniqueCount="2109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="2108">
   <si>
     <t>Seccion</t>
   </si>
@@ -6351,9 +6352,6 @@
   </si>
   <si>
     <t>Se agrego Modal de Ver requisicion para compras</t>
-  </si>
-  <si>
-    <t>Cambiar categoria por subcategoria y ponerla hasta arriba</t>
   </si>
 </sst>
 </file>
@@ -6551,44 +6549,6 @@
         <a:xfrm>
           <a:off x="4171950" y="3552825"/>
           <a:ext cx="3562847" cy="590632"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9692</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>581657</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>20188</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 4"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4191167" y="4162425"/>
-          <a:ext cx="3772365" cy="2801488"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7919,7 +7879,7 @@
       </c>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>149</v>
       </c>
@@ -7946,7 +7906,7 @@
       </c>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>149</v>
       </c>
@@ -9863,7 +9823,7 @@
       </c>
       <c r="I107" s="2"/>
     </row>
-    <row r="108" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>416</v>
       </c>
@@ -10700,7 +10660,7 @@
       </c>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>512</v>
       </c>
@@ -10727,7 +10687,7 @@
       </c>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>512</v>
       </c>
@@ -10889,7 +10849,7 @@
       </c>
       <c r="I145" s="2"/>
     </row>
-    <row r="146" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>534</v>
       </c>
@@ -14183,7 +14143,7 @@
       </c>
       <c r="I267" s="2"/>
     </row>
-    <row r="268" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>947</v>
       </c>
@@ -14669,7 +14629,7 @@
       </c>
       <c r="I285" s="2"/>
     </row>
-    <row r="286" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>1009</v>
       </c>
@@ -14696,7 +14656,7 @@
       </c>
       <c r="I286" s="2"/>
     </row>
-    <row r="287" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>1009</v>
       </c>
@@ -17277,7 +17237,7 @@
       </c>
       <c r="I381" s="2"/>
     </row>
-    <row r="382" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>1357</v>
       </c>
@@ -17304,7 +17264,7 @@
       </c>
       <c r="I382" s="2"/>
     </row>
-    <row r="383" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>1357</v>
       </c>
@@ -17331,7 +17291,7 @@
       </c>
       <c r="I383" s="2"/>
     </row>
-    <row r="384" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>1357</v>
       </c>
@@ -17358,7 +17318,7 @@
       </c>
       <c r="I384" s="2"/>
     </row>
-    <row r="385" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>1357</v>
       </c>
@@ -17682,7 +17642,7 @@
       </c>
       <c r="I396" s="2"/>
     </row>
-    <row r="397" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>1404</v>
       </c>
@@ -18762,7 +18722,7 @@
       </c>
       <c r="I436" s="2"/>
     </row>
-    <row r="437" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>1542</v>
       </c>
@@ -18978,7 +18938,7 @@
       </c>
       <c r="I444" s="2"/>
     </row>
-    <row r="445" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>1577</v>
       </c>
@@ -19059,7 +19019,7 @@
       </c>
       <c r="I447" s="2"/>
     </row>
-    <row r="448" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>1577</v>
       </c>
@@ -19086,7 +19046,7 @@
       </c>
       <c r="I448" s="2"/>
     </row>
-    <row r="449" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>1591</v>
       </c>
@@ -19167,7 +19127,7 @@
       </c>
       <c r="I451" s="2"/>
     </row>
-    <row r="452" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>1591</v>
       </c>
@@ -19518,7 +19478,7 @@
       </c>
       <c r="I464" s="2"/>
     </row>
-    <row r="465" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>1633</v>
       </c>
@@ -22050,9 +22010,7 @@
       </c>
     </row>
     <row r="8" spans="1:1" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>2108</v>
-      </c>
+      <c r="A8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
